--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,671 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123325621</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bränningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>601963</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6901251</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_1397</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera aspar, nära hyggeskant</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123325623</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79355</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bränningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601989</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6901207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_1396</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123325619</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78502</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bränningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601922</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6901279</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_1398</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kolade stubbe på hygge</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123325626</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bränningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602019</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6901151</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_1394</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123325625</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79384</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bränningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>602019</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6901176</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024_1395</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79720</v>
+        <v>79723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325621</v>
+        <v>123325623</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79358</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601963</v>
+        <v>601989</v>
       </c>
       <c r="R3" t="n">
-        <v>6901251</v>
+        <v>6901207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325623</v>
+        <v>123325626</v>
       </c>
       <c r="B4" t="n">
-        <v>79355</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,26 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601989</v>
+        <v>602019</v>
       </c>
       <c r="R4" t="n">
-        <v>6901207</v>
+        <v>6901151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1078,7 +1078,7 @@
         <v>123325619</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325626</v>
+        <v>123325621</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602019</v>
+        <v>601963</v>
       </c>
       <c r="R6" t="n">
-        <v>6901151</v>
+        <v>6901251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,7 +1348,7 @@
         <v>123325625</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79723</v>
+        <v>79725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123325623</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325626</v>
+        <v>123325619</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>78507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,26 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602019</v>
+        <v>601922</v>
       </c>
       <c r="R4" t="n">
-        <v>6901151</v>
+        <v>6901279</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325619</v>
+        <v>123325621</v>
       </c>
       <c r="B5" t="n">
-        <v>78505</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601922</v>
+        <v>601963</v>
       </c>
       <c r="R5" t="n">
-        <v>6901279</v>
+        <v>6901251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325621</v>
+        <v>123325625</v>
       </c>
       <c r="B6" t="n">
-        <v>79850</v>
+        <v>79389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601963</v>
+        <v>602019</v>
       </c>
       <c r="R6" t="n">
-        <v>6901251</v>
+        <v>6901176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1345,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325625</v>
+        <v>123325626</v>
       </c>
       <c r="B7" t="n">
-        <v>79387</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1361,26 +1356,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1397,7 +1392,7 @@
         <v>602019</v>
       </c>
       <c r="R7" t="n">
-        <v>6901176</v>
+        <v>6901151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,7 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123325623</v>
       </c>
       <c r="B3" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325619</v>
+        <v>123325625</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
+        <v>79390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,21 +956,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601922</v>
+        <v>602019</v>
       </c>
       <c r="R4" t="n">
-        <v>6901279</v>
+        <v>6901176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325621</v>
+        <v>123325619</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>78508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,26 +1086,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601963</v>
+        <v>601922</v>
       </c>
       <c r="R5" t="n">
-        <v>6901251</v>
+        <v>6901279</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325625</v>
+        <v>123325621</v>
       </c>
       <c r="B6" t="n">
-        <v>79389</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,26 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602019</v>
+        <v>601963</v>
       </c>
       <c r="R6" t="n">
-        <v>6901176</v>
+        <v>6901251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,7 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v>123325626</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
+        <v>79729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325623</v>
+        <v>123325626</v>
       </c>
       <c r="B3" t="n">
-        <v>79361</v>
+        <v>79856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601989</v>
+        <v>602019</v>
       </c>
       <c r="R3" t="n">
-        <v>6901207</v>
+        <v>6901151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325625</v>
+        <v>123325623</v>
       </c>
       <c r="B4" t="n">
-        <v>79390</v>
+        <v>79364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,21 +961,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602019</v>
+        <v>601989</v>
       </c>
       <c r="R4" t="n">
-        <v>6901176</v>
+        <v>6901207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325619</v>
+        <v>123325621</v>
       </c>
       <c r="B5" t="n">
-        <v>78508</v>
+        <v>79856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,26 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601922</v>
+        <v>601963</v>
       </c>
       <c r="R5" t="n">
-        <v>6901279</v>
+        <v>6901251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325621</v>
+        <v>123325625</v>
       </c>
       <c r="B6" t="n">
-        <v>79853</v>
+        <v>79393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,26 +1226,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601963</v>
+        <v>602019</v>
       </c>
       <c r="R6" t="n">
-        <v>6901251</v>
+        <v>6901176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325626</v>
+        <v>123325619</v>
       </c>
       <c r="B7" t="n">
-        <v>79853</v>
+        <v>78511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,26 +1356,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602019</v>
+        <v>601922</v>
       </c>
       <c r="R7" t="n">
-        <v>6901151</v>
+        <v>6901279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79729</v>
+        <v>79735</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325626</v>
+        <v>123325619</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>78517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602019</v>
+        <v>601922</v>
       </c>
       <c r="R3" t="n">
-        <v>6901151</v>
+        <v>6901279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325623</v>
+        <v>123325621</v>
       </c>
       <c r="B4" t="n">
-        <v>79364</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,26 +961,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601989</v>
+        <v>601963</v>
       </c>
       <c r="R4" t="n">
-        <v>6901207</v>
+        <v>6901251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325621</v>
+        <v>123325623</v>
       </c>
       <c r="B5" t="n">
-        <v>79856</v>
+        <v>79370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,26 +1096,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1124,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601963</v>
+        <v>601989</v>
       </c>
       <c r="R5" t="n">
-        <v>6901251</v>
+        <v>6901207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1179,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325625</v>
+        <v>123325626</v>
       </c>
       <c r="B6" t="n">
-        <v>79393</v>
+        <v>79862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1262,7 +1262,7 @@
         <v>602019</v>
       </c>
       <c r="R6" t="n">
-        <v>6901176</v>
+        <v>6901151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,7 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1334,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1340,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325619</v>
+        <v>123325625</v>
       </c>
       <c r="B7" t="n">
-        <v>78511</v>
+        <v>79399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,21 +1361,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601922</v>
+        <v>602019</v>
       </c>
       <c r="R7" t="n">
-        <v>6901279</v>
+        <v>6901176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1444,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79735</v>
+        <v>79740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123325619</v>
       </c>
       <c r="B3" t="n">
-        <v>78517</v>
+        <v>78522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325621</v>
+        <v>123325626</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601963</v>
+        <v>602019</v>
       </c>
       <c r="R4" t="n">
-        <v>6901251</v>
+        <v>6901151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,7 +1083,7 @@
         <v>123325623</v>
       </c>
       <c r="B5" t="n">
-        <v>79370</v>
+        <v>79375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325626</v>
+        <v>123325621</v>
       </c>
       <c r="B6" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602019</v>
+        <v>601963</v>
       </c>
       <c r="R6" t="n">
-        <v>6901151</v>
+        <v>6901251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,7 +1348,7 @@
         <v>123325625</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284491</v>
       </c>
       <c r="B2" t="n">
-        <v>79740</v>
+        <v>79742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325619</v>
+        <v>123325623</v>
       </c>
       <c r="B3" t="n">
-        <v>78522</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601922</v>
+        <v>601989</v>
       </c>
       <c r="R3" t="n">
-        <v>6901279</v>
+        <v>6901207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325626</v>
+        <v>123325625</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,26 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +992,7 @@
         <v>602019</v>
       </c>
       <c r="R4" t="n">
-        <v>6901151</v>
+        <v>6901176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325623</v>
+        <v>123325621</v>
       </c>
       <c r="B5" t="n">
-        <v>79375</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,26 +1086,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601989</v>
+        <v>601963</v>
       </c>
       <c r="R5" t="n">
-        <v>6901207</v>
+        <v>6901251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,7 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325621</v>
+        <v>123325619</v>
       </c>
       <c r="B6" t="n">
-        <v>79867</v>
+        <v>78524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,26 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601963</v>
+        <v>601922</v>
       </c>
       <c r="R6" t="n">
-        <v>6901251</v>
+        <v>6901279</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325625</v>
+        <v>123325626</v>
       </c>
       <c r="B7" t="n">
-        <v>79404</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1361,26 +1356,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1397,7 +1392,7 @@
         <v>602019</v>
       </c>
       <c r="R7" t="n">
-        <v>6901176</v>
+        <v>6901151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,7 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325623</v>
+        <v>123325621</v>
       </c>
       <c r="B3" t="n">
-        <v>79377</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601989</v>
+        <v>601963</v>
       </c>
       <c r="R3" t="n">
-        <v>6901207</v>
+        <v>6901251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1070,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325621</v>
+        <v>123325623</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,26 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601963</v>
+        <v>601989</v>
       </c>
       <c r="R5" t="n">
-        <v>6901251</v>
+        <v>6901207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325621</v>
+        <v>123325623</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601963</v>
+        <v>601989</v>
       </c>
       <c r="R3" t="n">
-        <v>6901251</v>
+        <v>6901207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1075,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325623</v>
+        <v>123325619</v>
       </c>
       <c r="B5" t="n">
-        <v>79377</v>
+        <v>78524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601989</v>
+        <v>601922</v>
       </c>
       <c r="R5" t="n">
-        <v>6901207</v>
+        <v>6901279</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,7 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325619</v>
+        <v>123325621</v>
       </c>
       <c r="B6" t="n">
-        <v>78524</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,26 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601922</v>
+        <v>601963</v>
       </c>
       <c r="R6" t="n">
-        <v>6901279</v>
+        <v>6901251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325623</v>
+        <v>123325626</v>
       </c>
       <c r="B3" t="n">
-        <v>79377</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601989</v>
+        <v>602019</v>
       </c>
       <c r="R3" t="n">
-        <v>6901207</v>
+        <v>6901151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325625</v>
+        <v>123325623</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,21 +961,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602019</v>
+        <v>601989</v>
       </c>
       <c r="R4" t="n">
-        <v>6901176</v>
+        <v>6901207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325619</v>
+        <v>123325621</v>
       </c>
       <c r="B5" t="n">
-        <v>78524</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,26 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601922</v>
+        <v>601963</v>
       </c>
       <c r="R5" t="n">
-        <v>6901279</v>
+        <v>6901251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325621</v>
+        <v>123325625</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,26 +1226,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601963</v>
+        <v>602019</v>
       </c>
       <c r="R6" t="n">
-        <v>6901251</v>
+        <v>6901176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325626</v>
+        <v>123325619</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>78524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,26 +1356,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602019</v>
+        <v>601922</v>
       </c>
       <c r="R7" t="n">
-        <v>6901151</v>
+        <v>6901279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325626</v>
+        <v>123325625</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>602019</v>
       </c>
       <c r="R3" t="n">
-        <v>6901151</v>
+        <v>6901176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325623</v>
+        <v>123325621</v>
       </c>
       <c r="B4" t="n">
-        <v>79377</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,26 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601989</v>
+        <v>601963</v>
       </c>
       <c r="R4" t="n">
-        <v>6901207</v>
+        <v>6901251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1397</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera aspar, nära hyggeskant</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325621</v>
+        <v>123325619</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>78524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601963</v>
+        <v>601922</v>
       </c>
       <c r="R5" t="n">
-        <v>6901251</v>
+        <v>6901279</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1397</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera aspar, nära hyggeskant</t>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325625</v>
+        <v>123325626</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1262,7 +1262,7 @@
         <v>602019</v>
       </c>
       <c r="R6" t="n">
-        <v>6901176</v>
+        <v>6901151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,7 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1334,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1340,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325619</v>
+        <v>123325623</v>
       </c>
       <c r="B7" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,21 +1361,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601922</v>
+        <v>601989</v>
       </c>
       <c r="R7" t="n">
-        <v>6901279</v>
+        <v>6901207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1444,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 42518-2023 artfynd.xlsx
+++ b/artfynd/A 42518-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325625</v>
+        <v>123325623</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602019</v>
+        <v>601989</v>
       </c>
       <c r="R3" t="n">
-        <v>6901176</v>
+        <v>6901207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1395</t>
+          <t>2024_1396</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325619</v>
+        <v>123325626</v>
       </c>
       <c r="B5" t="n">
-        <v>78524</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601922</v>
+        <v>602019</v>
       </c>
       <c r="R5" t="n">
-        <v>6901279</v>
+        <v>6901151</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1398</t>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolade stubbe på hygge</t>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325626</v>
+        <v>123325625</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1262,7 +1262,7 @@
         <v>602019</v>
       </c>
       <c r="R6" t="n">
-        <v>6901151</v>
+        <v>6901176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>2024_1395</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1345,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325623</v>
+        <v>123325619</v>
       </c>
       <c r="B7" t="n">
-        <v>79377</v>
+        <v>78524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1361,21 +1356,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601989</v>
+        <v>601922</v>
       </c>
       <c r="R7" t="n">
-        <v>6901207</v>
+        <v>6901279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1396</t>
+          <t>2024_1398</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,7 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kolade stubbe på hygge</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
